--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488032_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488032_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7</v>
+        <v>3.1314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7433</v>
+        <v>1.315</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9567</v>
+        <v>1.8163</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2569</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8975</v>
+        <v>-0.4662</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1232</v>
+        <v>-0.5514</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2256</v>
+        <v>0.0852</v>
       </c>
       <c r="V2" t="n">
         <v>1.2775</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3372</v>
+        <v>2.5687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8307</v>
+        <v>1.6358</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5065</v>
+        <v>0.9329</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5525</v>
+        <v>-2.5609</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3612</v>
+        <v>1.625</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.9138</v>
+        <v>-4.186</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7796</v>
+        <v>-1.8016</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2176</v>
+        <v>1.4735</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9972</v>
+        <v>-3.2751</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7729</v>
+        <v>-0.7593</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1437</v>
+        <v>0.1515</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9166</v>
+        <v>-0.9109</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3876</v>
+        <v>2.7751</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2267</v>
+        <v>-0.0091</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3349</v>
+        <v>-0.3999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8918</v>
+        <v>0.3908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2666</v>
+        <v>3.3547</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2666</v>
+        <v>4.8284</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>D. ABOY MARQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0426</v>
+        <v>0.9215</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1659</v>
+        <v>0.3825</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8767</v>
+        <v>0.539</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5609</v>
+        <v>0.6058</v>
       </c>
       <c r="H4" t="n">
-        <v>1.625</v>
+        <v>0.2461</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.186</v>
+        <v>0.3598</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8016</v>
+        <v>0.5303</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4735</v>
+        <v>0.0404</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.2751</v>
+        <v>0.4899</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7593</v>
+        <v>0.0756</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1515</v>
+        <v>0.2057</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9109</v>
+        <v>-0.1301</v>
       </c>
       <c r="P4" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7751</v>
+        <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5352</v>
+        <v>-0.279</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8698</v>
+        <v>-0.1477</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3346</v>
+        <v>-0.1313</v>
       </c>
       <c r="V4" t="n">
-        <v>3.3547</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.8284</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ABOY MARQUEZ</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.7321</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2807</v>
+        <v>-0.4936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4548</v>
+        <v>1.2257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6058</v>
+        <v>-1.5525</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2461</v>
+        <v>1.3612</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3598</v>
+        <v>-2.9138</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5303</v>
+        <v>-0.7796</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0404</v>
+        <v>1.2176</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4899</v>
+        <v>-1.9972</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0756</v>
+        <v>-0.7729</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2057</v>
+        <v>0.1437</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1301</v>
+        <v>-0.9166</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4651</v>
+        <v>1.6216</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2496</v>
+        <v>1.0106</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2155</v>
+        <v>0.611</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. PEÑA BAÑOS</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3027</v>
+        <v>0.3882</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3027</v>
+        <v>-0.6653</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.0535</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3027</v>
+        <v>-0.1156</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3027</v>
+        <v>0.156</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.2717</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3027</v>
+        <v>-0.659</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3027</v>
+        <v>0.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6791</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.5433</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.1358</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.4075</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3056</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0064</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>N. PEÑA BAÑOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9709</v>
+        <v>0.3027</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0535</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1156</v>
+        <v>0.3027</v>
       </c>
       <c r="H7" t="n">
-        <v>0.156</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2717</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.659</v>
+        <v>0.3027</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5433</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1358</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4075</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.312</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3994</v>
+        <v>-0.917</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4935</v>
+        <v>-3.5946</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0941</v>
+        <v>2.6776</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4628</v>
+        <v>-4.6231</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4724</v>
+        <v>-1.2062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009599999999999999</v>
+        <v>-3.4169</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5673</v>
+        <v>-3.9939</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4182</v>
+        <v>-0.6786</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.149</v>
+        <v>-3.3153</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1045</v>
+        <v>-0.6292</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0542</v>
+        <v>-0.5276</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1586</v>
+        <v>-0.1016</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>2.7751</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1805</v>
+        <v>3.7662</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1317</v>
+        <v>-0.2761</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7894</v>
+        <v>-0.0833</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3423</v>
+        <v>-0.1929</v>
       </c>
       <c r="V8" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4737</v>
+      </c>
+      <c r="X8" t="n">
         <v>-0.2666</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.2666</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.5331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8631</v>
+        <v>-0.9411</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1476</v>
+        <v>-2.8386</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2845</v>
+        <v>1.8975</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6231</v>
+        <v>-1.4628</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2062</v>
+        <v>-1.4724</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.4169</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.9939</v>
+        <v>-1.5673</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6786</v>
+        <v>-1.4182</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.3153</v>
+        <v>-0.149</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6292</v>
+        <v>0.1045</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5276</v>
+        <v>-0.0542</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1016</v>
+        <v>0.1586</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7751</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7662</v>
+        <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2223</v>
+        <v>0.5901</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3637</v>
+        <v>0.4444</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.586</v>
+        <v>0.1457</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2071</v>
+        <v>-0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2173</v>
+        <v>-1.9994</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6228</v>
+        <v>-0.295</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4055</v>
+        <v>-1.7044</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.862</v>
+        <v>-1.0379</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6132</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2488</v>
+        <v>-0.3922</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3494</v>
+        <v>0.0124</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3494</v>
+        <v>-0.5177</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.5301</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-1.0503</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2638</v>
+        <v>-0.128</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2488</v>
+        <v>-0.9223</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9822</v>
+        <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5764</v>
+        <v>-0.7277</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4333</v>
+        <v>-0.3073</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1431</v>
+        <v>-0.4204</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9405</v>
+        <v>-2.4142</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>J. GIANNETTO DE LEON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3736</v>
+        <v>-2.493</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7254</v>
+        <v>-3.5153</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6483</v>
+        <v>1.0223</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0379</v>
+        <v>-2.8569</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.7008</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3922</v>
+        <v>-2.1561</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0124</v>
+        <v>-2.6762</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5177</v>
+        <v>-0.6388</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5301</v>
+        <v>-2.0374</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0503</v>
+        <v>-0.1807</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.128</v>
+        <v>-0.062</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9223</v>
+        <v>-0.1187</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1805</v>
+        <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.102</v>
+        <v>-0.1009</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7377</v>
+        <v>-0.1146</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3642</v>
+        <v>0.0137</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4142</v>
+        <v>0.2666</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GIANNETTO DE LEON</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3175</v>
+        <v>-2.7661</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0871</v>
+        <v>-3.1716</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7696</v>
+        <v>0.4055</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8569</v>
+        <v>-0.862</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7008</v>
+        <v>-0.6132</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1561</v>
+        <v>-0.2488</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6762</v>
+        <v>-0.3494</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6388</v>
+        <v>-0.3494</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0374</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1807</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.062</v>
+        <v>-0.2638</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1187</v>
+        <v>-0.2488</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9254</v>
+        <v>0.0276</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6864</v>
+        <v>-0.1155</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.239</v>
+        <v>0.1431</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2666</v>
+        <v>-0.9405</v>
       </c>
       <c r="W12" t="n">
         <v>0.2666</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.3674</v>
+        <v>-6.6419</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.7704</v>
+        <v>-10.9325</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4029</v>
+        <v>4.2906</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1516</v>
@@ -1468,13 +1468,13 @@
         <v>3.9645</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8699</v>
+        <v>-1.1444</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9233</v>
+        <v>-1.0854</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0534</v>
+        <v>-0.0589</v>
       </c>
       <c r="V13" t="n">
         <v>-0.337</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.3378</v>
+        <v>-7.713899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.4944</v>
+        <v>-21.8705</v>
       </c>
       <c r="F14" t="n">
         <v>14.1565</v>
@@ -1546,16 +1546,16 @@
         <v>22.7957</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0826</v>
+        <v>-0.4585000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9807</v>
+        <v>-1.3565</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8980999999999999</v>
+        <v>0.898</v>
       </c>
       <c r="V14" t="n">
-        <v>2.414199999999999</v>
+        <v>2.4142</v>
       </c>
       <c r="W14" t="n">
         <v>7.901600000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. GARCIA GAZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1855</v>
+        <v>5.5132</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2192</v>
+        <v>2.1282</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9662</v>
+        <v>3.385</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8703</v>
+        <v>5.6809</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5709</v>
+        <v>1.7456</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2995</v>
+        <v>3.9353</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4625</v>
+        <v>3.3351</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5384</v>
+        <v>1.3185</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9241</v>
+        <v>2.0167</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4078</v>
+        <v>2.3458</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0324</v>
+        <v>0.4271</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3754</v>
+        <v>1.9187</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R15" t="n">
         <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3063</v>
+        <v>0.0743</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1969</v>
+        <v>-0.1898</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1093</v>
+        <v>0.2641</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5331</v>
+        <v>2.9474</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5331</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GARCIA GAZQUEZ</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3273</v>
+        <v>3.7482</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4152</v>
+        <v>-0.5957</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9122</v>
+        <v>4.3439</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6809</v>
+        <v>3.8703</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7456</v>
+        <v>1.5709</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9353</v>
+        <v>2.2995</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3351</v>
+        <v>1.4625</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3185</v>
+        <v>0.5384</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0167</v>
+        <v>0.9241</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3458</v>
+        <v>2.4078</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4271</v>
+        <v>1.0324</v>
       </c>
       <c r="O16" t="n">
-        <v>1.9187</v>
+        <v>1.3754</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R16" t="n">
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1116</v>
+        <v>0.869</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9029</v>
+        <v>0.382</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2087</v>
+        <v>0.487</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9474</v>
+        <v>0.5331</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2071</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9263</v>
+        <v>3.3469</v>
       </c>
       <c r="E17" t="n">
-        <v>0.648</v>
+        <v>1.1573</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2784</v>
+        <v>2.1896</v>
       </c>
       <c r="G17" t="n">
         <v>3.4873</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1646</v>
+        <v>0.256</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4771</v>
+        <v>0.0322</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3125</v>
+        <v>0.2237</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.157</v>
+        <v>1.6277</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0427</v>
+        <v>-0.4085</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1143</v>
+        <v>2.0361</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4036</v>
+        <v>2.2991</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2372</v>
+        <v>-1.0128</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1664</v>
+        <v>3.3119</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7871</v>
+        <v>0.8671</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4105</v>
+        <v>-1.3583</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1975</v>
+        <v>2.2253</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1907</v>
+        <v>1.4321</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8267</v>
+        <v>0.3455</v>
       </c>
       <c r="O18" t="n">
-        <v>1.364</v>
+        <v>1.0866</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.899</v>
+        <v>-0.2661</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8298</v>
+        <v>-0.2844</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0692</v>
+        <v>0.0183</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1367</v>
+        <v>-0.6036</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1367</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3116</v>
+        <v>1.4158</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6122</v>
+        <v>-0.6704</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9238</v>
+        <v>2.0862</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2991</v>
+        <v>1.4036</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0128</v>
+        <v>1.2372</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3119</v>
+        <v>0.1664</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8671</v>
+        <v>-0.7871</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3583</v>
+        <v>0.4105</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2253</v>
+        <v>-1.1975</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4321</v>
+        <v>2.1907</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3455</v>
+        <v>0.8267</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0866</v>
+        <v>1.364</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5822000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4881</v>
+        <v>0.1167</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.094</v>
+        <v>0.0411</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6036</v>
+        <v>-1.1367</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6036</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9356</v>
+        <v>1.1661</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3346</v>
+        <v>0.2327</v>
       </c>
       <c r="F21" t="n">
-        <v>0.601</v>
+        <v>0.9334</v>
       </c>
       <c r="G21" t="n">
         <v>0.5168</v>
@@ -2092,13 +2092,13 @@
         <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2889</v>
+        <v>0.5194</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4406</v>
+        <v>0.3387</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1516</v>
+        <v>0.1807</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2666</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3134</v>
+        <v>-0.3487</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.617</v>
+        <v>-1.8207</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3036</v>
+        <v>1.472</v>
       </c>
       <c r="G22" t="n">
         <v>0.6117</v>
@@ -2170,13 +2170,13 @@
         <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2621</v>
+        <v>-0.2973</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0072</v>
+        <v>-0.211</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2548</v>
+        <v>-0.0864</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SANCHEZ BARRERA</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7153</v>
+        <v>-0.6528</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8663</v>
+        <v>-2.2272</v>
       </c>
       <c r="F23" t="n">
-        <v>0.151</v>
+        <v>1.5743</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7451</v>
+        <v>1.7351</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7451</v>
+        <v>1.0119</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.7232</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6791</v>
+        <v>0.6117</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6791</v>
+        <v>1.3997</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.788</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.066</v>
+        <v>1.1233</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.066</v>
+        <v>-0.3879</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.5112</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1685</v>
+        <v>0.5854</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1872</v>
+        <v>-0.0815</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0187</v>
+        <v>0.667</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>A. SANCHEZ BARRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0309</v>
+        <v>-0.6873</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.329</v>
+        <v>-0.8663</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2981</v>
+        <v>0.1791</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7351</v>
+        <v>-0.7451</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0119</v>
+        <v>-0.7451</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7232</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6117</v>
+        <v>-0.6791</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3997</v>
+        <v>-0.6791</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.788</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1233</v>
+        <v>-0.066</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3879</v>
+        <v>-0.066</v>
       </c>
       <c r="O24" t="n">
-        <v>1.5112</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9733</v>
+        <v>0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2074</v>
+        <v>-0.1404</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1834</v>
+        <v>-0.1872</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3908</v>
+        <v>0.0468</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.917</v>
+        <v>-1.9346</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1808</v>
+        <v>-5.2827</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2638</v>
+        <v>3.3481</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8241000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3</v>
+        <v>-0.3176</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2458</v>
+        <v>-0.3477</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0542</v>
+        <v>0.0301</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.0395</v>
+        <v>-5.6882</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.7215</v>
+        <v>-7.314</v>
       </c>
       <c r="F26" t="n">
-        <v>1.682</v>
+        <v>1.6258</v>
       </c>
       <c r="G26" t="n">
         <v>1.0256</v>
@@ -2482,13 +2482,13 @@
         <v>0.7929</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0302</v>
+        <v>0.3211</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8736</v>
+        <v>-0.4661</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8434</v>
+        <v>0.7872</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8811</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.337900000000003</v>
+        <v>9.017000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.1564</v>
+        <v>-14.1566</v>
       </c>
       <c r="F27" t="n">
-        <v>22.4944</v>
+        <v>23.1735</v>
       </c>
       <c r="G27" t="n">
         <v>20.5719</v>
@@ -2533,7 +2533,7 @@
         <v>16.1281</v>
       </c>
       <c r="J27" t="n">
-        <v>4.0499</v>
+        <v>4.049899999999999</v>
       </c>
       <c r="K27" t="n">
         <v>1.5899</v>
@@ -2560,13 +2560,13 @@
         <v>11.8932</v>
       </c>
       <c r="S27" t="n">
-        <v>1.0824</v>
+        <v>1.7616</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.898</v>
+        <v>-0.8981</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9806</v>
+        <v>2.6596</v>
       </c>
       <c r="V27" t="n">
         <v>-2.4143</v>
@@ -2575,7 +2575,7 @@
         <v>5.4873</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.901599999999999</v>
+        <v>-7.901600000000001</v>
       </c>
     </row>
   </sheetData>
